--- a/AAII_Financials/Yearly/JG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JG_YR_FIN.xlsx
@@ -2217,13 +2217,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>700</v>
@@ -2370,13 +2370,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G45" s="3">
         <v>900</v>
